--- a/DMCH-IITD.xlsx
+++ b/DMCH-IITD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8560e7807dac39fc/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="385" documentId="8_{B03A5FCC-0E31-4F65-BFC7-8B5009A26463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F311E15-D6C9-4D43-8EB9-EB4B394D8505}"/>
+  <xr:revisionPtr revIDLastSave="431" documentId="8_{B03A5FCC-0E31-4F65-BFC7-8B5009A26463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8016EE13-0FA9-4357-AA1C-224DF2006CC8}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{49B68CEF-1206-43AF-A1CC-270024516C35}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{49B68CEF-1206-43AF-A1CC-270024516C35}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -289,13 +289,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="20"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -310,6 +303,13 @@
       <name val="Aptos Display"/>
       <family val="2"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -354,23 +354,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -713,30 +714,30 @@
   <dimension ref="A1:BZ2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.85546875" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" customWidth="1"/>
     <col min="5" max="5" width="9.7109375" customWidth="1"/>
-    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="16.28515625" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" customWidth="1"/>
+    <col min="9" max="9" width="17.140625" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" customWidth="1"/>
+    <col min="11" max="11" width="18.140625" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="9.85546875" customWidth="1"/>
     <col min="14" max="14" width="9" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="9.5703125" customWidth="1"/>
     <col min="17" max="17" width="19.5703125" customWidth="1"/>
     <col min="18" max="18" width="11.28515625" customWidth="1"/>
-    <col min="19" max="19" width="14.140625" customWidth="1"/>
-    <col min="20" max="20" width="12.5703125" customWidth="1"/>
+    <col min="19" max="19" width="16.5703125" customWidth="1"/>
+    <col min="20" max="20" width="15.7109375" customWidth="1"/>
     <col min="21" max="21" width="9" bestFit="1" customWidth="1"/>
     <col min="22" max="23" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.7109375" customWidth="1"/>
-    <col min="25" max="25" width="10.85546875" customWidth="1"/>
+    <col min="24" max="24" width="13.140625" customWidth="1"/>
+    <col min="25" max="25" width="16" customWidth="1"/>
     <col min="26" max="26" width="9" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.42578125" customWidth="1"/>
-    <col min="28" max="28" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="17.5703125" customWidth="1"/>
+    <col min="28" max="28" width="7.5703125" customWidth="1"/>
     <col min="29" max="29" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="8.85546875" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="6.5703125" customWidth="1"/>
@@ -751,27 +752,32 @@
     <col min="44" max="44" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="11" customWidth="1"/>
     <col min="46" max="46" width="10.140625" customWidth="1"/>
-    <col min="47" max="47" width="13.85546875" customWidth="1"/>
+    <col min="47" max="47" width="17" customWidth="1"/>
     <col min="48" max="48" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="49" max="49" width="11" customWidth="1"/>
     <col min="50" max="50" width="11.140625" customWidth="1"/>
-    <col min="51" max="51" width="9" bestFit="1" customWidth="1"/>
-    <col min="53" max="54" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="55" max="56" width="9" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="11" customWidth="1"/>
+    <col min="53" max="53" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="54" max="55" width="11.7109375" customWidth="1"/>
+    <col min="56" max="56" width="11" customWidth="1"/>
+    <col min="57" max="57" width="11.28515625" customWidth="1"/>
+    <col min="58" max="58" width="10.85546875" customWidth="1"/>
     <col min="59" max="59" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="9" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="10.85546875" customWidth="1"/>
     <col min="63" max="64" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="18.140625" customWidth="1"/>
-    <col min="66" max="66" width="12.42578125" customWidth="1"/>
+    <col min="65" max="65" width="25.42578125" customWidth="1"/>
+    <col min="66" max="66" width="15.140625" customWidth="1"/>
     <col min="67" max="67" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="68" max="68" width="15.5703125" customWidth="1"/>
     <col min="69" max="69" width="15.42578125" customWidth="1"/>
-    <col min="70" max="70" width="19" customWidth="1"/>
-    <col min="71" max="71" width="8" bestFit="1" customWidth="1"/>
-    <col min="72" max="76" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="11" customWidth="1"/>
+    <col min="70" max="70" width="22" customWidth="1"/>
+    <col min="71" max="71" width="8.85546875" customWidth="1"/>
+    <col min="72" max="72" width="11.85546875" customWidth="1"/>
+    <col min="73" max="73" width="10.5703125" customWidth="1"/>
+    <col min="74" max="74" width="9.5703125" customWidth="1"/>
+    <col min="75" max="75" width="9.85546875" customWidth="1"/>
+    <col min="76" max="76" width="10.140625" customWidth="1"/>
+    <col min="77" max="77" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:78" s="2" customFormat="1" ht="173.25" x14ac:dyDescent="0.25">
@@ -1007,15 +1013,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:78" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:78" s="5" customFormat="1" ht="21" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D2" s="3">
         <v>0</v>
@@ -1029,50 +1035,50 @@
       <c r="G2" s="3">
         <v>0</v>
       </c>
-      <c r="H2" s="4">
-        <v>1</v>
+      <c r="H2" s="3">
+        <v>0</v>
       </c>
       <c r="I2" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="3">
         <v>0</v>
       </c>
       <c r="L2" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N2" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O2" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P2" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R2" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S2" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T2" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" s="3">
         <v>0</v>
       </c>
       <c r="V2" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W2" s="3">
         <v>0</v>
@@ -1081,7 +1087,7 @@
         <v>0</v>
       </c>
       <c r="Y2" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z2" s="3">
         <v>0</v>
@@ -1090,31 +1096,31 @@
         <v>0</v>
       </c>
       <c r="AB2" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC2" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" s="3">
         <v>0</v>
       </c>
       <c r="AE2" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF2" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AG2" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH2" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI2" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ2" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK2" s="3">
         <v>0</v>
@@ -1135,7 +1141,7 @@
         <v>0</v>
       </c>
       <c r="AQ2" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR2" s="3">
         <v>0</v>
@@ -1171,19 +1177,19 @@
         <v>0</v>
       </c>
       <c r="BC2" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD2" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BE2" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF2" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG2" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BH2" s="3">
         <v>0</v>
@@ -1195,10 +1201,10 @@
         <v>0</v>
       </c>
       <c r="BK2" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL2" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM2" s="3">
         <v>0</v>
@@ -1216,10 +1222,10 @@
         <v>0</v>
       </c>
       <c r="BR2" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BS2" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT2" s="3">
         <v>0</v>
@@ -1239,7 +1245,7 @@
       <c r="BY2" s="3">
         <v>0</v>
       </c>
-      <c r="BZ2" s="3"/>
+      <c r="BZ2" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">
